--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260817.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260817.xlsx
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>遠東銀</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2,648,000</t>
+          <t>99,084,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>遠東銀</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>99,084,000</t>
+          <t>2,648,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>12,795,000</t>
+          <t>21,744,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>21,744,000</t>
+          <t>12,795,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
